--- a/data/sugerencias_historico.xlsx
+++ b/data/sugerencias_historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.2494</v>
+        <v>2.0645</v>
       </c>
       <c r="D2" t="n">
         <v>116</v>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.2229</v>
+        <v>2.0468</v>
       </c>
       <c r="D3" t="n">
         <v>103</v>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.1523</v>
+        <v>1.987</v>
       </c>
       <c r="D4" t="n">
         <v>121</v>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.6975</v>
+        <v>1.5728</v>
       </c>
       <c r="D5" t="n">
         <v>115</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.8014</v>
+        <v>1.6693</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.6775</v>
+        <v>1.5708</v>
       </c>
       <c r="D7" t="n">
         <v>101</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.455</v>
+        <v>2.2494</v>
       </c>
       <c r="D8" t="n">
         <v>116</v>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.4189</v>
+        <v>2.2229</v>
       </c>
       <c r="D9" t="n">
         <v>103</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.3362</v>
+        <v>2.1523</v>
       </c>
       <c r="D10" t="n">
         <v>121</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.8362</v>
+        <v>1.6975</v>
       </c>
       <c r="D11" t="n">
         <v>115</v>
@@ -826,14 +826,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.9843</v>
+        <v>1.8014</v>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -856,14 +856,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.9484</v>
+        <v>1.6775</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.6835</v>
+        <v>2.2494</v>
       </c>
       <c r="D14" t="n">
         <v>116</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.6367</v>
+        <v>2.2229</v>
       </c>
       <c r="D15" t="n">
         <v>103</v>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.5406</v>
+        <v>2.1523</v>
       </c>
       <c r="D16" t="n">
         <v>121</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.9904</v>
+        <v>1.6975</v>
       </c>
       <c r="D17" t="n">
         <v>115</v>
@@ -1030,14 +1030,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.1415</v>
+        <v>1.8014</v>
       </c>
       <c r="D18" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1060,14 +1060,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.1117</v>
+        <v>1.6775</v>
       </c>
       <c r="D19" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.6835</v>
+        <v>2.455</v>
       </c>
       <c r="D20" t="n">
         <v>116</v>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.6367</v>
+        <v>2.4189</v>
       </c>
       <c r="D21" t="n">
         <v>103</v>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.5406</v>
+        <v>2.3362</v>
       </c>
       <c r="D22" t="n">
         <v>121</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.9904</v>
+        <v>1.8362</v>
       </c>
       <c r="D23" t="n">
         <v>115</v>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.1415</v>
+        <v>1.9843</v>
       </c>
       <c r="D24" t="n">
         <v>102</v>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.1117</v>
+        <v>1.9484</v>
       </c>
       <c r="D25" t="n">
         <v>96</v>
@@ -4753,6 +4753,414 @@
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D128" t="n">
+        <v>116</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>3</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D129" t="n">
+        <v>103</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>15</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D130" t="n">
+        <v>121</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>13</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D131" t="n">
+        <v>115</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>10</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D132" t="n">
+        <v>102</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D133" t="n">
+        <v>96</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D134" t="n">
+        <v>116</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D135" t="n">
+        <v>103</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>15</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D136" t="n">
+        <v>121</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>13</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D137" t="n">
+        <v>115</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D138" t="n">
+        <v>102</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D139" t="n">
+        <v>96</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sugerencias_historico.xlsx
+++ b/data/sugerencias_historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,14 +478,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.0645</v>
+        <v>1.1257</v>
       </c>
       <c r="D2" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.0468</v>
+        <v>1.1147</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.987</v>
+        <v>1.1376</v>
       </c>
       <c r="D4" t="n">
         <v>121</v>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.5728</v>
+        <v>0.9319</v>
       </c>
       <c r="D5" t="n">
         <v>115</v>
@@ -622,14 +622,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.6693</v>
+        <v>1.0222</v>
       </c>
       <c r="D6" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -652,14 +652,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.5708</v>
+        <v>0.8776</v>
       </c>
       <c r="D7" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2494</v>
+        <v>1.1944</v>
       </c>
       <c r="D8" t="n">
         <v>116</v>
@@ -718,14 +718,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.2229</v>
+        <v>1.191</v>
       </c>
       <c r="D9" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.1523</v>
+        <v>1.2088</v>
       </c>
       <c r="D10" t="n">
         <v>121</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.6975</v>
+        <v>0.9856</v>
       </c>
       <c r="D11" t="n">
         <v>115</v>
@@ -826,14 +826,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.8014</v>
+        <v>1.0683</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -856,14 +856,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.6775</v>
+        <v>0.9322</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.2494</v>
+        <v>1.2828</v>
       </c>
       <c r="D14" t="n">
         <v>116</v>
@@ -922,14 +922,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.2229</v>
+        <v>1.2632</v>
       </c>
       <c r="D15" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.1523</v>
+        <v>1.2878</v>
       </c>
       <c r="D16" t="n">
         <v>121</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.6975</v>
+        <v>1.0452</v>
       </c>
       <c r="D17" t="n">
         <v>115</v>
@@ -1030,14 +1030,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.8014</v>
+        <v>1.1193</v>
       </c>
       <c r="D18" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1060,14 +1060,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.6775</v>
+        <v>0.9925</v>
       </c>
       <c r="D19" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.455</v>
+        <v>1.3812</v>
       </c>
       <c r="D20" t="n">
         <v>116</v>
@@ -1126,14 +1126,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.4189</v>
+        <v>1.3439</v>
       </c>
       <c r="D21" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.3362</v>
+        <v>1.3759</v>
       </c>
       <c r="D22" t="n">
         <v>121</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.8362</v>
+        <v>1.1117</v>
       </c>
       <c r="D23" t="n">
         <v>115</v>
@@ -1234,14 +1234,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.9843</v>
+        <v>1.1762</v>
       </c>
       <c r="D24" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.9484</v>
+        <v>1.0599</v>
       </c>
       <c r="D25" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1294,14 +1294,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[10, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.6835</v>
+        <v>1.4996</v>
       </c>
       <c r="D26" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1330,14 +1330,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.6367</v>
+        <v>1.4905</v>
       </c>
       <c r="D27" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.5406</v>
+        <v>1.4735</v>
       </c>
       <c r="D28" t="n">
         <v>121</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.9904</v>
+        <v>1.1853</v>
       </c>
       <c r="D29" t="n">
         <v>115</v>
@@ -1438,14 +1438,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.1415</v>
+        <v>1.2392</v>
       </c>
       <c r="D30" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1468,14 +1468,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.1117</v>
+        <v>1.1344</v>
       </c>
       <c r="D31" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1498,14 +1498,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[10, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.6835</v>
+        <v>1.6156</v>
       </c>
       <c r="D32" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1534,14 +1534,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.6367</v>
+        <v>1.6122</v>
       </c>
       <c r="D33" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.5406</v>
+        <v>1.5824</v>
       </c>
       <c r="D34" t="n">
         <v>121</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.9904</v>
+        <v>1.2675</v>
       </c>
       <c r="D35" t="n">
         <v>115</v>
@@ -1642,14 +1642,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.1415</v>
+        <v>1.3096</v>
       </c>
       <c r="D36" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1672,14 +1672,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2.1117</v>
+        <v>1.2176</v>
       </c>
       <c r="D37" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.6835</v>
+        <v>1.7473</v>
       </c>
       <c r="D38" t="n">
         <v>116</v>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.6367</v>
+        <v>1.7444</v>
       </c>
       <c r="D39" t="n">
         <v>103</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.5406</v>
+        <v>1.7032</v>
       </c>
       <c r="D40" t="n">
         <v>121</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.9904</v>
+        <v>1.3587</v>
       </c>
       <c r="D41" t="n">
         <v>115</v>
@@ -1846,14 +1846,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.1415</v>
+        <v>1.4423</v>
       </c>
       <c r="D42" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1876,14 +1876,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.1117</v>
+        <v>1.3875</v>
       </c>
       <c r="D43" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.6835</v>
+        <v>1.8975</v>
       </c>
       <c r="D44" t="n">
         <v>116</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.6367</v>
+        <v>1.8875</v>
       </c>
       <c r="D45" t="n">
         <v>103</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.5406</v>
+        <v>1.8376</v>
       </c>
       <c r="D46" t="n">
         <v>121</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.9904</v>
+        <v>1.4601</v>
       </c>
       <c r="D47" t="n">
         <v>115</v>
@@ -2050,14 +2050,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.1415</v>
+        <v>1.5498</v>
       </c>
       <c r="D48" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2080,14 +2080,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.1117</v>
+        <v>1.4744</v>
       </c>
       <c r="D49" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.6835</v>
+        <v>2.0645</v>
       </c>
       <c r="D50" t="n">
         <v>116</v>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.6367</v>
+        <v>2.0468</v>
       </c>
       <c r="D51" t="n">
         <v>103</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.5406</v>
+        <v>1.987</v>
       </c>
       <c r="D52" t="n">
         <v>121</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.9904</v>
+        <v>1.5728</v>
       </c>
       <c r="D53" t="n">
         <v>115</v>
@@ -2254,14 +2254,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.1415</v>
+        <v>1.6693</v>
       </c>
       <c r="D54" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2284,14 +2284,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.1117</v>
+        <v>1.5708</v>
       </c>
       <c r="D55" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.6835</v>
+        <v>2.2494</v>
       </c>
       <c r="D56" t="n">
         <v>116</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.6367</v>
+        <v>2.2229</v>
       </c>
       <c r="D57" t="n">
         <v>103</v>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.5406</v>
+        <v>2.1523</v>
       </c>
       <c r="D58" t="n">
         <v>121</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.9904</v>
+        <v>1.6975</v>
       </c>
       <c r="D59" t="n">
         <v>115</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2.1415</v>
+        <v>1.8014</v>
       </c>
       <c r="D60" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2.1117</v>
+        <v>1.6775</v>
       </c>
       <c r="D61" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.6835</v>
+        <v>2.2494</v>
       </c>
       <c r="D62" t="n">
         <v>116</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.6367</v>
+        <v>2.2229</v>
       </c>
       <c r="D63" t="n">
         <v>103</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.5406</v>
+        <v>2.1523</v>
       </c>
       <c r="D64" t="n">
         <v>121</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.9904</v>
+        <v>1.6975</v>
       </c>
       <c r="D65" t="n">
         <v>115</v>
@@ -2662,14 +2662,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.1415</v>
+        <v>1.8014</v>
       </c>
       <c r="D66" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.1117</v>
+        <v>1.6775</v>
       </c>
       <c r="D67" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.6835</v>
+        <v>2.455</v>
       </c>
       <c r="D68" t="n">
         <v>116</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.6367</v>
+        <v>2.4189</v>
       </c>
       <c r="D69" t="n">
         <v>103</v>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.5406</v>
+        <v>2.3362</v>
       </c>
       <c r="D70" t="n">
         <v>121</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.9904</v>
+        <v>1.8362</v>
       </c>
       <c r="D71" t="n">
         <v>115</v>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2.1415</v>
+        <v>1.9843</v>
       </c>
       <c r="D72" t="n">
         <v>102</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.1117</v>
+        <v>1.9484</v>
       </c>
       <c r="D73" t="n">
         <v>96</v>
@@ -5161,6 +5161,1638 @@
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D140" t="n">
+        <v>116</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D141" t="n">
+        <v>103</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>15</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D142" t="n">
+        <v>121</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>13</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D143" t="n">
+        <v>115</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>10</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D144" t="n">
+        <v>102</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D145" t="n">
+        <v>96</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D146" t="n">
+        <v>116</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>3</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D147" t="n">
+        <v>103</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>15</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D148" t="n">
+        <v>121</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>13</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D149" t="n">
+        <v>115</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>10</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D150" t="n">
+        <v>102</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D151" t="n">
+        <v>96</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D152" t="n">
+        <v>116</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>3</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D153" t="n">
+        <v>103</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>15</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D154" t="n">
+        <v>121</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>13</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D155" t="n">
+        <v>115</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>10</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D156" t="n">
+        <v>102</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D157" t="n">
+        <v>96</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D158" t="n">
+        <v>116</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>3</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D159" t="n">
+        <v>103</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>15</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D160" t="n">
+        <v>121</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>13</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D161" t="n">
+        <v>115</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>10</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D162" t="n">
+        <v>102</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D163" t="n">
+        <v>96</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D164" t="n">
+        <v>116</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>3</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D165" t="n">
+        <v>103</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>15</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D166" t="n">
+        <v>121</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>13</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D167" t="n">
+        <v>115</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>10</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D168" t="n">
+        <v>102</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D169" t="n">
+        <v>96</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D170" t="n">
+        <v>116</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>3</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D171" t="n">
+        <v>103</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>15</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D172" t="n">
+        <v>121</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>13</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D173" t="n">
+        <v>115</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>10</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D174" t="n">
+        <v>102</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D175" t="n">
+        <v>96</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D176" t="n">
+        <v>116</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>3</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D177" t="n">
+        <v>103</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>15</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D178" t="n">
+        <v>121</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>13</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D179" t="n">
+        <v>115</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>10</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D180" t="n">
+        <v>102</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D181" t="n">
+        <v>96</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D182" t="n">
+        <v>116</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D183" t="n">
+        <v>103</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>15</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D184" t="n">
+        <v>121</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>13</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D185" t="n">
+        <v>115</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>10</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D186" t="n">
+        <v>102</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D187" t="n">
+        <v>96</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sugerencias_historico.xlsx
+++ b/data/sugerencias_historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,14 +478,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.1257</v>
+        <v>0.8374</v>
       </c>
       <c r="D2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.1147</v>
+        <v>0.7413</v>
       </c>
       <c r="D3" t="n">
         <v>116</v>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.1376</v>
+        <v>0.8034</v>
       </c>
       <c r="D4" t="n">
         <v>121</v>
@@ -586,14 +586,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9319</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.0222</v>
+        <v>0.7684</v>
       </c>
       <c r="D6" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -652,14 +652,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[1, 5, 17, 26, 37]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8776</v>
+        <v>0.6383</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -682,14 +682,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.1944</v>
+        <v>0.8666</v>
       </c>
       <c r="D8" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -718,14 +718,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.191</v>
+        <v>0.7795</v>
       </c>
       <c r="D9" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.2088</v>
+        <v>0.8375</v>
       </c>
       <c r="D10" t="n">
         <v>121</v>
@@ -790,14 +790,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9856</v>
+        <v>0.5863</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -826,14 +826,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.0683</v>
+        <v>0.797</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -856,14 +856,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[10, 21, 25, 26, 28]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9322</v>
+        <v>0.6974</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -886,14 +886,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.2828</v>
+        <v>0.8666</v>
       </c>
       <c r="D14" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -922,14 +922,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.2632</v>
+        <v>0.7795</v>
       </c>
       <c r="D15" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.2878</v>
+        <v>0.8375</v>
       </c>
       <c r="D16" t="n">
         <v>121</v>
@@ -994,14 +994,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.0452</v>
+        <v>0.5863</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1030,14 +1030,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.1193</v>
+        <v>0.797</v>
       </c>
       <c r="D18" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1060,14 +1060,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[10, 21, 25, 26, 28]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9925</v>
+        <v>0.6974</v>
       </c>
       <c r="D19" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1090,14 +1090,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.3812</v>
+        <v>0.8986</v>
       </c>
       <c r="D20" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1126,14 +1126,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.3439</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3759</v>
+        <v>0.8749</v>
       </c>
       <c r="D22" t="n">
         <v>121</v>
@@ -1198,14 +1198,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 22, 36, 39]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.1117</v>
+        <v>0.5933</v>
       </c>
       <c r="D23" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1234,14 +1234,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.1762</v>
+        <v>0.8284</v>
       </c>
       <c r="D24" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.0599</v>
+        <v>0.8071</v>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1294,14 +1294,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.4996</v>
+        <v>0.9353</v>
       </c>
       <c r="D26" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.4905</v>
+        <v>0.8689</v>
       </c>
       <c r="D27" t="n">
         <v>116</v>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.4735</v>
+        <v>0.9175</v>
       </c>
       <c r="D28" t="n">
         <v>121</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.1853</v>
+        <v>0.766</v>
       </c>
       <c r="D29" t="n">
         <v>115</v>
@@ -1438,14 +1438,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2392</v>
+        <v>0.8642</v>
       </c>
       <c r="D30" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1468,14 +1468,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.1344</v>
+        <v>0.8363</v>
       </c>
       <c r="D31" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1498,14 +1498,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.6156</v>
+        <v>0.975</v>
       </c>
       <c r="D32" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.6122</v>
+        <v>0.9208</v>
       </c>
       <c r="D33" t="n">
         <v>116</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.5824</v>
+        <v>0.964</v>
       </c>
       <c r="D34" t="n">
         <v>121</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.2675</v>
+        <v>0.8008</v>
       </c>
       <c r="D35" t="n">
         <v>115</v>
@@ -1642,14 +1642,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.3096</v>
+        <v>0.8679</v>
       </c>
       <c r="D36" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1672,14 +1672,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.2176</v>
+        <v>0.7524</v>
       </c>
       <c r="D37" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1702,14 +1702,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.7473</v>
+        <v>0.975</v>
       </c>
       <c r="D38" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1738,14 +1738,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.7444</v>
+        <v>0.9208</v>
       </c>
       <c r="D39" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.7032</v>
+        <v>0.964</v>
       </c>
       <c r="D40" t="n">
         <v>121</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.3587</v>
+        <v>0.8008</v>
       </c>
       <c r="D41" t="n">
         <v>115</v>
@@ -1846,14 +1846,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.4423</v>
+        <v>0.8679</v>
       </c>
       <c r="D42" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1876,14 +1876,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.3875</v>
+        <v>0.7524</v>
       </c>
       <c r="D43" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1906,14 +1906,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.8975</v>
+        <v>0.975</v>
       </c>
       <c r="D44" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1942,14 +1942,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.8875</v>
+        <v>0.9208</v>
       </c>
       <c r="D45" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.8376</v>
+        <v>0.964</v>
       </c>
       <c r="D46" t="n">
         <v>121</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.4601</v>
+        <v>0.8008</v>
       </c>
       <c r="D47" t="n">
         <v>115</v>
@@ -2050,14 +2050,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.5498</v>
+        <v>0.8679</v>
       </c>
       <c r="D48" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2080,14 +2080,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.4744</v>
+        <v>0.7524</v>
       </c>
       <c r="D49" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.0645</v>
+        <v>1.0139</v>
       </c>
       <c r="D50" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2146,14 +2146,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.0468</v>
+        <v>0.9782</v>
       </c>
       <c r="D51" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.987</v>
+        <v>1.0154</v>
       </c>
       <c r="D52" t="n">
         <v>121</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.5728</v>
+        <v>0.8395</v>
       </c>
       <c r="D53" t="n">
         <v>115</v>
@@ -2254,14 +2254,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.6693</v>
+        <v>0.9434</v>
       </c>
       <c r="D54" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2284,14 +2284,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[5, 13, 26, 27, 38]</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.5708</v>
+        <v>0.9325</v>
       </c>
       <c r="D55" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2314,14 +2314,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2.2494</v>
+        <v>0.975</v>
       </c>
       <c r="D56" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.2229</v>
+        <v>0.9208</v>
       </c>
       <c r="D57" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2.1523</v>
+        <v>0.964</v>
       </c>
       <c r="D58" t="n">
         <v>121</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.6975</v>
+        <v>0.8008</v>
       </c>
       <c r="D59" t="n">
         <v>115</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1.8014</v>
+        <v>0.8679</v>
       </c>
       <c r="D60" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.6775</v>
+        <v>0.7524</v>
       </c>
       <c r="D61" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2518,14 +2518,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.2494</v>
+        <v>1.0139</v>
       </c>
       <c r="D62" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2554,14 +2554,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.2229</v>
+        <v>0.9782</v>
       </c>
       <c r="D63" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.1523</v>
+        <v>1.0154</v>
       </c>
       <c r="D64" t="n">
         <v>121</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.6975</v>
+        <v>0.8395</v>
       </c>
       <c r="D65" t="n">
         <v>115</v>
@@ -2662,14 +2662,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.8014</v>
+        <v>0.9434</v>
       </c>
       <c r="D66" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[5, 13, 26, 27, 38]</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1.6775</v>
+        <v>0.9325</v>
       </c>
       <c r="D67" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.455</v>
+        <v>1.0667</v>
       </c>
       <c r="D68" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2758,14 +2758,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.4189</v>
+        <v>1.0427</v>
       </c>
       <c r="D69" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2.3362</v>
+        <v>1.0731</v>
       </c>
       <c r="D70" t="n">
         <v>121</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.8362</v>
+        <v>0.8831</v>
       </c>
       <c r="D71" t="n">
         <v>115</v>
@@ -2866,14 +2866,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 23, 26, 29]</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.9843</v>
+        <v>1.0145</v>
       </c>
       <c r="D72" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 11, 15, 16, 37]</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.9484</v>
+        <v>0.8582</v>
       </c>
       <c r="D73" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2926,14 +2926,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.6835</v>
+        <v>1.1257</v>
       </c>
       <c r="D74" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2962,14 +2962,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.6367</v>
+        <v>1.1147</v>
       </c>
       <c r="D75" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2.5406</v>
+        <v>1.1376</v>
       </c>
       <c r="D76" t="n">
         <v>121</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.9904</v>
+        <v>0.9319</v>
       </c>
       <c r="D77" t="n">
         <v>115</v>
@@ -3070,14 +3070,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2.1415</v>
+        <v>1.0222</v>
       </c>
       <c r="D78" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3100,14 +3100,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2.1117</v>
+        <v>0.8776</v>
       </c>
       <c r="D79" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2.6835</v>
+        <v>1.1944</v>
       </c>
       <c r="D80" t="n">
         <v>116</v>
@@ -3166,14 +3166,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.6367</v>
+        <v>1.191</v>
       </c>
       <c r="D81" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2.5406</v>
+        <v>1.2088</v>
       </c>
       <c r="D82" t="n">
         <v>121</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.9904</v>
+        <v>0.9856</v>
       </c>
       <c r="D83" t="n">
         <v>115</v>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2.1415</v>
+        <v>1.0683</v>
       </c>
       <c r="D84" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3304,14 +3304,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2.1117</v>
+        <v>0.9322</v>
       </c>
       <c r="D85" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2.6835</v>
+        <v>1.2828</v>
       </c>
       <c r="D86" t="n">
         <v>116</v>
@@ -3370,14 +3370,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.6367</v>
+        <v>1.2632</v>
       </c>
       <c r="D87" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2.5406</v>
+        <v>1.2878</v>
       </c>
       <c r="D88" t="n">
         <v>121</v>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.9904</v>
+        <v>1.0452</v>
       </c>
       <c r="D89" t="n">
         <v>115</v>
@@ -3478,14 +3478,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2.1415</v>
+        <v>1.1193</v>
       </c>
       <c r="D90" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3508,14 +3508,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2.1117</v>
+        <v>0.9925</v>
       </c>
       <c r="D91" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2.6835</v>
+        <v>1.3812</v>
       </c>
       <c r="D92" t="n">
         <v>116</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2.6367</v>
+        <v>1.3439</v>
       </c>
       <c r="D93" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2.5406</v>
+        <v>1.3759</v>
       </c>
       <c r="D94" t="n">
         <v>121</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.9904</v>
+        <v>1.1117</v>
       </c>
       <c r="D95" t="n">
         <v>115</v>
@@ -3682,14 +3682,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2.1415</v>
+        <v>1.1762</v>
       </c>
       <c r="D96" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3712,14 +3712,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2.1117</v>
+        <v>1.0599</v>
       </c>
       <c r="D97" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[10, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2.6835</v>
+        <v>1.4996</v>
       </c>
       <c r="D98" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3778,14 +3778,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2.6367</v>
+        <v>1.4905</v>
       </c>
       <c r="D99" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2.5406</v>
+        <v>1.4735</v>
       </c>
       <c r="D100" t="n">
         <v>121</v>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.9904</v>
+        <v>1.1853</v>
       </c>
       <c r="D101" t="n">
         <v>115</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2.1415</v>
+        <v>1.2392</v>
       </c>
       <c r="D102" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3916,14 +3916,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2.1117</v>
+        <v>1.1344</v>
       </c>
       <c r="D103" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3946,14 +3946,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[10, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2.6835</v>
+        <v>1.6156</v>
       </c>
       <c r="D104" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3982,14 +3982,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2.6367</v>
+        <v>1.6122</v>
       </c>
       <c r="D105" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2.5406</v>
+        <v>1.5824</v>
       </c>
       <c r="D106" t="n">
         <v>121</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.9904</v>
+        <v>1.2675</v>
       </c>
       <c r="D107" t="n">
         <v>115</v>
@@ -4090,14 +4090,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2.1415</v>
+        <v>1.3096</v>
       </c>
       <c r="D108" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4120,14 +4120,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2.1117</v>
+        <v>1.2176</v>
       </c>
       <c r="D109" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2.6835</v>
+        <v>1.7473</v>
       </c>
       <c r="D110" t="n">
         <v>116</v>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2.6367</v>
+        <v>1.7444</v>
       </c>
       <c r="D111" t="n">
         <v>103</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2.5406</v>
+        <v>1.7032</v>
       </c>
       <c r="D112" t="n">
         <v>121</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1.9904</v>
+        <v>1.3587</v>
       </c>
       <c r="D113" t="n">
         <v>115</v>
@@ -4294,14 +4294,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2.1415</v>
+        <v>1.4423</v>
       </c>
       <c r="D114" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4324,14 +4324,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2.1117</v>
+        <v>1.3875</v>
       </c>
       <c r="D115" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2.6835</v>
+        <v>1.8975</v>
       </c>
       <c r="D116" t="n">
         <v>116</v>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2.6367</v>
+        <v>1.8875</v>
       </c>
       <c r="D117" t="n">
         <v>103</v>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2.5406</v>
+        <v>1.8376</v>
       </c>
       <c r="D118" t="n">
         <v>121</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.9904</v>
+        <v>1.4601</v>
       </c>
       <c r="D119" t="n">
         <v>115</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2.1415</v>
+        <v>1.5498</v>
       </c>
       <c r="D120" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2.1117</v>
+        <v>1.4744</v>
       </c>
       <c r="D121" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2.6835</v>
+        <v>2.0645</v>
       </c>
       <c r="D122" t="n">
         <v>116</v>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2.6367</v>
+        <v>2.0468</v>
       </c>
       <c r="D123" t="n">
         <v>103</v>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2.5406</v>
+        <v>1.987</v>
       </c>
       <c r="D124" t="n">
         <v>121</v>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1.9904</v>
+        <v>1.5728</v>
       </c>
       <c r="D125" t="n">
         <v>115</v>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2.1415</v>
+        <v>1.6693</v>
       </c>
       <c r="D126" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4732,14 +4732,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2.1117</v>
+        <v>1.5708</v>
       </c>
       <c r="D127" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2.6835</v>
+        <v>2.2494</v>
       </c>
       <c r="D128" t="n">
         <v>116</v>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2.6367</v>
+        <v>2.2229</v>
       </c>
       <c r="D129" t="n">
         <v>103</v>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2.5406</v>
+        <v>2.1523</v>
       </c>
       <c r="D130" t="n">
         <v>121</v>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1.9904</v>
+        <v>1.6975</v>
       </c>
       <c r="D131" t="n">
         <v>115</v>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2.1415</v>
+        <v>1.8014</v>
       </c>
       <c r="D132" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4936,14 +4936,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2.1117</v>
+        <v>1.6775</v>
       </c>
       <c r="D133" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2.6835</v>
+        <v>2.2494</v>
       </c>
       <c r="D134" t="n">
         <v>116</v>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2.6367</v>
+        <v>2.2229</v>
       </c>
       <c r="D135" t="n">
         <v>103</v>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2.5406</v>
+        <v>2.1523</v>
       </c>
       <c r="D136" t="n">
         <v>121</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1.9904</v>
+        <v>1.6975</v>
       </c>
       <c r="D137" t="n">
         <v>115</v>
@@ -5110,14 +5110,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2.1415</v>
+        <v>1.8014</v>
       </c>
       <c r="D138" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5140,14 +5140,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2.1117</v>
+        <v>1.6775</v>
       </c>
       <c r="D139" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2.6835</v>
+        <v>2.455</v>
       </c>
       <c r="D140" t="n">
         <v>116</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2.6367</v>
+        <v>2.4189</v>
       </c>
       <c r="D141" t="n">
         <v>103</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2.5406</v>
+        <v>2.3362</v>
       </c>
       <c r="D142" t="n">
         <v>121</v>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1.9904</v>
+        <v>1.8362</v>
       </c>
       <c r="D143" t="n">
         <v>115</v>
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2.1415</v>
+        <v>1.9843</v>
       </c>
       <c r="D144" t="n">
         <v>102</v>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2.1117</v>
+        <v>1.9484</v>
       </c>
       <c r="D145" t="n">
         <v>96</v>
@@ -6793,6 +6793,2454 @@
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D188" t="n">
+        <v>116</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>3</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D189" t="n">
+        <v>103</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>15</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D190" t="n">
+        <v>121</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>13</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D191" t="n">
+        <v>115</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>10</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D192" t="n">
+        <v>102</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D193" t="n">
+        <v>96</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D194" t="n">
+        <v>116</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>3</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D195" t="n">
+        <v>103</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>15</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D196" t="n">
+        <v>121</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>13</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D197" t="n">
+        <v>115</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>10</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D198" t="n">
+        <v>102</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D199" t="n">
+        <v>96</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D200" t="n">
+        <v>116</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>3</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D201" t="n">
+        <v>103</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>15</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D202" t="n">
+        <v>121</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>13</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D203" t="n">
+        <v>115</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>10</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D204" t="n">
+        <v>102</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D205" t="n">
+        <v>96</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D206" t="n">
+        <v>116</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>3</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D207" t="n">
+        <v>103</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>15</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D208" t="n">
+        <v>121</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>13</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D209" t="n">
+        <v>115</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>10</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D210" t="n">
+        <v>102</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D211" t="n">
+        <v>96</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D212" t="n">
+        <v>116</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D213" t="n">
+        <v>103</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>15</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D214" t="n">
+        <v>121</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>13</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D215" t="n">
+        <v>115</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>10</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D216" t="n">
+        <v>102</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D217" t="n">
+        <v>96</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D218" t="n">
+        <v>116</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>3</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D219" t="n">
+        <v>103</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>15</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D220" t="n">
+        <v>121</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>13</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D221" t="n">
+        <v>115</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>10</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D222" t="n">
+        <v>102</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D223" t="n">
+        <v>96</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D224" t="n">
+        <v>116</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>3</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D225" t="n">
+        <v>103</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>15</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D226" t="n">
+        <v>121</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>13</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D227" t="n">
+        <v>115</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>10</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D228" t="n">
+        <v>102</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D229" t="n">
+        <v>96</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D230" t="n">
+        <v>116</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>3</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D231" t="n">
+        <v>103</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>15</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D232" t="n">
+        <v>121</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>13</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D233" t="n">
+        <v>115</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>10</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D234" t="n">
+        <v>102</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D235" t="n">
+        <v>96</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D236" t="n">
+        <v>116</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>3</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D237" t="n">
+        <v>103</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>15</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D238" t="n">
+        <v>121</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>13</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D239" t="n">
+        <v>115</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>10</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D240" t="n">
+        <v>102</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D241" t="n">
+        <v>96</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D242" t="n">
+        <v>116</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>3</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D243" t="n">
+        <v>103</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>15</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D244" t="n">
+        <v>121</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>13</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D245" t="n">
+        <v>115</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>10</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D246" t="n">
+        <v>102</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D247" t="n">
+        <v>96</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D248" t="n">
+        <v>116</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>3</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D249" t="n">
+        <v>103</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>15</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D250" t="n">
+        <v>121</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>13</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D251" t="n">
+        <v>115</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>10</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D252" t="n">
+        <v>102</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D253" t="n">
+        <v>96</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D254" t="n">
+        <v>116</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>3</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D255" t="n">
+        <v>103</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>15</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D256" t="n">
+        <v>121</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>13</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D257" t="n">
+        <v>115</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>10</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D258" t="n">
+        <v>102</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D259" t="n">
+        <v>96</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sugerencias_historico.xlsx
+++ b/data/sugerencias_historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,14 +478,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[4, 8, 15, 30, 37]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8374</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -494,11 +494,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[6, 18, 22, 28, 35]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7413</v>
+        <v>0.7148</v>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -530,11 +530,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[4, 7, 20, 38, 42]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8034</v>
+        <v>0.5812</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -566,11 +566,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,14 +586,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[8, 9, 21, 36, 39]</t>
+          <t>[5, 6, 23, 29, 32]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.3874</v>
       </c>
       <c r="D5" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -602,11 +602,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[3, 8, 21, 30, 36]</t>
+          <t>[3, 16, 25, 32, 38]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7684</v>
+        <v>0.6065</v>
       </c>
       <c r="D6" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -652,14 +652,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 5, 17, 26, 37]</t>
+          <t>[11, 14, 22, 26, 27]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6383</v>
+        <v>0.5747</v>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -682,14 +682,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[4, 8, 15, 30, 37]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8666</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -698,11 +698,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -718,14 +718,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[6, 18, 22, 28, 35]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7795</v>
+        <v>0.7148</v>
       </c>
       <c r="D9" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -734,11 +734,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -754,14 +754,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[4, 7, 20, 38, 42]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8375</v>
+        <v>0.5812</v>
       </c>
       <c r="D10" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -770,11 +770,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -790,14 +790,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[8, 9, 21, 36, 39]</t>
+          <t>[5, 6, 23, 29, 32]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5863</v>
+        <v>0.3874</v>
       </c>
       <c r="D11" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -806,11 +806,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -826,14 +826,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[3, 8, 21, 30, 36]</t>
+          <t>[3, 16, 25, 32, 38]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.797</v>
+        <v>0.6065</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -856,14 +856,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 28]</t>
+          <t>[11, 14, 22, 26, 27]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6974</v>
+        <v>0.5747</v>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -886,14 +886,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[4, 8, 15, 30, 37]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8666</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -902,11 +902,11 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -922,14 +922,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[6, 18, 22, 28, 35]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7795</v>
+        <v>0.7148</v>
       </c>
       <c r="D15" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -938,11 +938,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -958,14 +958,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[4, 7, 20, 38, 42]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8375</v>
+        <v>0.5812</v>
       </c>
       <c r="D16" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -974,11 +974,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -994,14 +994,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[8, 9, 21, 36, 39]</t>
+          <t>[5, 6, 23, 29, 32]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5863</v>
+        <v>0.3874</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1030,14 +1030,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[3, 8, 21, 30, 36]</t>
+          <t>[3, 16, 25, 32, 38]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.797</v>
+        <v>0.6065</v>
       </c>
       <c r="D18" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1060,14 +1060,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 28]</t>
+          <t>[11, 14, 22, 26, 27]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6974</v>
+        <v>0.5747</v>
       </c>
       <c r="D19" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1090,14 +1090,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[4, 8, 15, 30, 37]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.8986</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1106,11 +1106,11 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1126,14 +1126,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[6, 18, 22, 28, 35]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.7148</v>
       </c>
       <c r="D21" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1142,11 +1142,11 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[4, 7, 20, 38, 42]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.8749</v>
+        <v>0.5812</v>
       </c>
       <c r="D22" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 36, 39]</t>
+          <t>[5, 6, 23, 29, 32]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.5933</v>
+        <v>0.3874</v>
       </c>
       <c r="D23" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1234,14 +1234,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[3, 8, 21, 30, 36]</t>
+          <t>[3, 16, 25, 32, 38]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.8284</v>
+        <v>0.6065</v>
       </c>
       <c r="D24" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1264,14 +1264,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 29]</t>
+          <t>[11, 14, 22, 26, 27]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.8071</v>
+        <v>0.5747</v>
       </c>
       <c r="D25" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1294,14 +1294,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[4, 8, 15, 30, 37]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9353</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1310,11 +1310,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1330,14 +1330,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[6, 18, 22, 28, 35]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.8689</v>
+        <v>0.7148</v>
       </c>
       <c r="D27" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1346,11 +1346,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1366,14 +1366,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[4, 7, 20, 38, 42]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9175</v>
+        <v>0.5812</v>
       </c>
       <c r="D28" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1402,14 +1402,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[5, 6, 23, 29, 32]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.766</v>
+        <v>0.3874</v>
       </c>
       <c r="D29" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1438,14 +1438,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[3, 8, 21, 30, 36]</t>
+          <t>[3, 16, 25, 32, 38]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.8642</v>
+        <v>0.6065</v>
       </c>
       <c r="D30" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1468,14 +1468,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 29]</t>
+          <t>[11, 14, 22, 26, 27]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8363</v>
+        <v>0.5747</v>
       </c>
       <c r="D31" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1498,14 +1498,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[4, 8, 15, 30, 37]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.975</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1514,11 +1514,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1534,14 +1534,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[6, 18, 22, 28, 35]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9208</v>
+        <v>0.7148</v>
       </c>
       <c r="D33" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1570,14 +1570,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[4, 7, 20, 38, 42]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.964</v>
+        <v>0.5812</v>
       </c>
       <c r="D34" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1586,11 +1586,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[5, 6, 23, 29, 32]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.8008</v>
+        <v>0.3874</v>
       </c>
       <c r="D35" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1622,11 +1622,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1642,14 +1642,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 29]</t>
+          <t>[3, 16, 25, 32, 38]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.8679</v>
+        <v>0.6065</v>
       </c>
       <c r="D36" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1672,14 +1672,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 5, 17, 26, 38]</t>
+          <t>[11, 14, 22, 26, 27]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.7524</v>
+        <v>0.5747</v>
       </c>
       <c r="D37" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1702,14 +1702,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[4, 8, 15, 30, 37]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.975</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1718,11 +1718,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1738,14 +1738,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[6, 18, 22, 28, 35]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9208</v>
+        <v>0.7148</v>
       </c>
       <c r="D39" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1774,14 +1774,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[4, 7, 20, 38, 42]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.964</v>
+        <v>0.5812</v>
       </c>
       <c r="D40" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1790,11 +1790,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1810,14 +1810,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[5, 6, 23, 29, 32]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.8008</v>
+        <v>0.3874</v>
       </c>
       <c r="D41" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1826,11 +1826,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1846,14 +1846,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 29]</t>
+          <t>[3, 16, 25, 32, 38]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.8679</v>
+        <v>0.6065</v>
       </c>
       <c r="D42" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -1876,14 +1876,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 5, 17, 26, 38]</t>
+          <t>[11, 14, 22, 26, 27]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.7524</v>
+        <v>0.5747</v>
       </c>
       <c r="D43" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -1906,14 +1906,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[9, 14, 21, 28, 34]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.975</v>
+        <v>0.711</v>
       </c>
       <c r="D44" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1942,14 +1942,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[11, 17, 23, 28, 38]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9208</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1978,14 +1978,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[15, 18, 21, 28, 38]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.964</v>
+        <v>0.7019</v>
       </c>
       <c r="D46" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2014,14 +2014,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 15, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.8008</v>
+        <v>0.542</v>
       </c>
       <c r="D47" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2050,14 +2050,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.8679</v>
+        <v>0.6597</v>
       </c>
       <c r="D48" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2080,14 +2080,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 5, 17, 26, 38]</t>
+          <t>[5, 11, 15, 24, 37]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.7524</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 34]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.0139</v>
+        <v>0.711</v>
       </c>
       <c r="D50" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2146,14 +2146,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[11, 17, 23, 28, 38]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9782</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2182,14 +2182,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[15, 18, 22, 28, 38]</t>
+          <t>[15, 18, 21, 28, 38]</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.0154</v>
+        <v>0.7019</v>
       </c>
       <c r="D52" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2218,14 +2218,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 15, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.8395</v>
+        <v>0.542</v>
       </c>
       <c r="D53" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2254,14 +2254,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.9434</v>
+        <v>0.6597</v>
       </c>
       <c r="D54" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2284,14 +2284,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[5, 13, 26, 27, 38]</t>
+          <t>[5, 11, 15, 24, 37]</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9325</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2314,14 +2314,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>[9, 14, 21, 28, 29]</t>
+          <t>[9, 14, 21, 28, 34]</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.975</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[11, 17, 23, 28, 38]</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.9208</v>
+        <v>0.7022</v>
       </c>
       <c r="D57" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.964</v>
+        <v>0.6761</v>
       </c>
       <c r="D58" t="n">
         <v>121</v>
@@ -2422,14 +2422,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 15, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.8008</v>
+        <v>0.5419</v>
       </c>
       <c r="D59" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[10, 21, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.8679</v>
+        <v>0.6603</v>
       </c>
       <c r="D60" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[1, 5, 17, 26, 38]</t>
+          <t>[5, 11, 15, 24, 37]</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.7524</v>
+        <v>0.5517</v>
       </c>
       <c r="D61" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2518,14 +2518,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 34]</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1.0139</v>
+        <v>0.7168</v>
       </c>
       <c r="D62" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2554,14 +2554,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[11, 17, 23, 28, 38]</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.9782</v>
+        <v>0.7071</v>
       </c>
       <c r="D63" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1.0154</v>
+        <v>0.6833</v>
       </c>
       <c r="D64" t="n">
         <v>121</v>
@@ -2626,14 +2626,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 15, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.8395</v>
+        <v>0.5462</v>
       </c>
       <c r="D65" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2662,14 +2662,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.9434</v>
+        <v>0.6666</v>
       </c>
       <c r="D66" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>[5, 13, 26, 27, 38]</t>
+          <t>[5, 11, 15, 24, 37]</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.9325</v>
+        <v>0.5532</v>
       </c>
       <c r="D67" t="n">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 34]</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.0667</v>
+        <v>0.7304</v>
       </c>
       <c r="D68" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2758,14 +2758,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[11, 17, 24, 28, 38]</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.0427</v>
+        <v>0.7168</v>
       </c>
       <c r="D69" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.0731</v>
+        <v>0.6988</v>
       </c>
       <c r="D70" t="n">
         <v>121</v>
@@ -2830,14 +2830,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.8831</v>
+        <v>0.5114</v>
       </c>
       <c r="D71" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2866,14 +2866,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[10, 11, 23, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.0145</v>
+        <v>0.6805</v>
       </c>
       <c r="D72" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2896,14 +2896,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[5, 11, 15, 16, 37]</t>
+          <t>[5, 11, 15, 24, 37]</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.8582</v>
+        <v>0.5606</v>
       </c>
       <c r="D73" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2926,14 +2926,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.1257</v>
+        <v>0.7664</v>
       </c>
       <c r="D74" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.1147</v>
+        <v>0.6489</v>
       </c>
       <c r="D75" t="n">
         <v>116</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.1376</v>
+        <v>0.7206</v>
       </c>
       <c r="D76" t="n">
         <v>121</v>
@@ -3034,14 +3034,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.9319</v>
+        <v>0.5233</v>
       </c>
       <c r="D77" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3070,14 +3070,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.0222</v>
+        <v>0.6989</v>
       </c>
       <c r="D78" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3100,14 +3100,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[1, 5, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.8776</v>
+        <v>0.5901</v>
       </c>
       <c r="D79" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3130,14 +3130,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.1944</v>
+        <v>0.7879</v>
       </c>
       <c r="D80" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3166,14 +3166,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.191</v>
+        <v>0.6768</v>
       </c>
       <c r="D81" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.2088</v>
+        <v>0.7456</v>
       </c>
       <c r="D82" t="n">
         <v>121</v>
@@ -3238,14 +3238,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.9856</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="D83" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.0683</v>
+        <v>0.7199</v>
       </c>
       <c r="D84" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3304,14 +3304,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[1, 5, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.9322</v>
+        <v>0.6078</v>
       </c>
       <c r="D85" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3334,14 +3334,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.2828</v>
+        <v>0.8111</v>
       </c>
       <c r="D86" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3370,14 +3370,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.2632</v>
+        <v>0.7073</v>
       </c>
       <c r="D87" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.2878</v>
+        <v>0.773</v>
       </c>
       <c r="D88" t="n">
         <v>121</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.0452</v>
+        <v>0.5514</v>
       </c>
       <c r="D89" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3478,14 +3478,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.1193</v>
+        <v>0.7429</v>
       </c>
       <c r="D90" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3508,14 +3508,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[1, 5, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.9925</v>
+        <v>0.6269</v>
       </c>
       <c r="D91" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3538,14 +3538,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.3812</v>
+        <v>0.8374</v>
       </c>
       <c r="D92" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[9, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.3439</v>
+        <v>0.7413</v>
       </c>
       <c r="D93" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.3759</v>
+        <v>0.8034</v>
       </c>
       <c r="D94" t="n">
         <v>121</v>
@@ -3646,14 +3646,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.1117</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="D95" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3682,14 +3682,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.1762</v>
+        <v>0.7684</v>
       </c>
       <c r="D96" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3712,14 +3712,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[1, 5, 17, 26, 37]</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.0599</v>
+        <v>0.6383</v>
       </c>
       <c r="D97" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.4996</v>
+        <v>0.8666</v>
       </c>
       <c r="D98" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.4905</v>
+        <v>0.7795</v>
       </c>
       <c r="D99" t="n">
         <v>116</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.4735</v>
+        <v>0.8375</v>
       </c>
       <c r="D100" t="n">
         <v>121</v>
@@ -3850,14 +3850,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1.1853</v>
+        <v>0.5863</v>
       </c>
       <c r="D101" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1.2392</v>
+        <v>0.797</v>
       </c>
       <c r="D102" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3916,14 +3916,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[10, 21, 25, 26, 28]</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1.1344</v>
+        <v>0.6974</v>
       </c>
       <c r="D103" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3946,14 +3946,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.6156</v>
+        <v>0.8666</v>
       </c>
       <c r="D104" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.6122</v>
+        <v>0.7795</v>
       </c>
       <c r="D105" t="n">
         <v>116</v>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1.5824</v>
+        <v>0.8375</v>
       </c>
       <c r="D106" t="n">
         <v>121</v>
@@ -4054,14 +4054,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 21, 36, 39]</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.2675</v>
+        <v>0.5863</v>
       </c>
       <c r="D107" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4090,14 +4090,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1.3096</v>
+        <v>0.797</v>
       </c>
       <c r="D108" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4120,14 +4120,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 25, 37]</t>
+          <t>[10, 21, 25, 26, 28]</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.2176</v>
+        <v>0.6974</v>
       </c>
       <c r="D109" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4150,14 +4150,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1.7473</v>
+        <v>0.8986</v>
       </c>
       <c r="D110" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -4186,14 +4186,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1.7444</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="D111" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1.7032</v>
+        <v>0.8749</v>
       </c>
       <c r="D112" t="n">
         <v>121</v>
@@ -4258,14 +4258,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[8, 9, 22, 37, 39]</t>
+          <t>[8, 9, 22, 36, 39]</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1.3587</v>
+        <v>0.5933</v>
       </c>
       <c r="D113" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4294,14 +4294,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1.4423</v>
+        <v>0.8284</v>
       </c>
       <c r="D114" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4324,14 +4324,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.3875</v>
+        <v>0.8071</v>
       </c>
       <c r="D115" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4354,14 +4354,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1.8975</v>
+        <v>0.9353</v>
       </c>
       <c r="D116" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4390,14 +4390,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.8875</v>
+        <v>0.8689</v>
       </c>
       <c r="D117" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.8376</v>
+        <v>0.9175</v>
       </c>
       <c r="D118" t="n">
         <v>121</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1.4601</v>
+        <v>0.766</v>
       </c>
       <c r="D119" t="n">
         <v>115</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[3, 8, 21, 30, 36]</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1.5498</v>
+        <v>0.8642</v>
       </c>
       <c r="D120" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1.4744</v>
+        <v>0.8363</v>
       </c>
       <c r="D121" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4558,14 +4558,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2.0645</v>
+        <v>0.975</v>
       </c>
       <c r="D122" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -4594,14 +4594,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2.0468</v>
+        <v>0.9208</v>
       </c>
       <c r="D123" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1.987</v>
+        <v>0.964</v>
       </c>
       <c r="D124" t="n">
         <v>121</v>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1.5728</v>
+        <v>0.8008</v>
       </c>
       <c r="D125" t="n">
         <v>115</v>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1.6693</v>
+        <v>0.8679</v>
       </c>
       <c r="D126" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4732,14 +4732,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1.5708</v>
+        <v>0.7524</v>
       </c>
       <c r="D127" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4762,14 +4762,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2.2494</v>
+        <v>0.975</v>
       </c>
       <c r="D128" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -4798,14 +4798,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2.2229</v>
+        <v>0.9208</v>
       </c>
       <c r="D129" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2.1523</v>
+        <v>0.964</v>
       </c>
       <c r="D130" t="n">
         <v>121</v>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1.6975</v>
+        <v>0.8008</v>
       </c>
       <c r="D131" t="n">
         <v>115</v>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1.8014</v>
+        <v>0.8679</v>
       </c>
       <c r="D132" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4936,14 +4936,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1.6775</v>
+        <v>0.7524</v>
       </c>
       <c r="D133" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4966,14 +4966,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2.2494</v>
+        <v>0.975</v>
       </c>
       <c r="D134" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -5002,14 +5002,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2.2229</v>
+        <v>0.9208</v>
       </c>
       <c r="D135" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2.1523</v>
+        <v>0.964</v>
       </c>
       <c r="D136" t="n">
         <v>121</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1.6975</v>
+        <v>0.8008</v>
       </c>
       <c r="D137" t="n">
         <v>115</v>
@@ -5110,14 +5110,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1.8014</v>
+        <v>0.8679</v>
       </c>
       <c r="D138" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5140,14 +5140,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[10, 11, 25, 26, 29]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1.6775</v>
+        <v>0.7524</v>
       </c>
       <c r="D139" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5170,14 +5170,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2.455</v>
+        <v>1.0139</v>
       </c>
       <c r="D140" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -5206,14 +5206,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2.4189</v>
+        <v>0.9782</v>
       </c>
       <c r="D141" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2.3362</v>
+        <v>1.0154</v>
       </c>
       <c r="D142" t="n">
         <v>121</v>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1.8362</v>
+        <v>0.8395</v>
       </c>
       <c r="D143" t="n">
         <v>115</v>
@@ -5314,14 +5314,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1.9843</v>
+        <v>0.9434</v>
       </c>
       <c r="D144" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5344,14 +5344,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 13, 26, 27, 38]</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1.9484</v>
+        <v>0.9325</v>
       </c>
       <c r="D145" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5374,14 +5374,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 21, 28, 29]</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2.6835</v>
+        <v>0.975</v>
       </c>
       <c r="D146" t="n">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5410,14 +5410,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2.6367</v>
+        <v>0.9208</v>
       </c>
       <c r="D147" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2.5406</v>
+        <v>0.964</v>
       </c>
       <c r="D148" t="n">
         <v>121</v>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1.9904</v>
+        <v>0.8008</v>
       </c>
       <c r="D149" t="n">
         <v>115</v>
@@ -5518,14 +5518,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 21, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2.1415</v>
+        <v>0.8679</v>
       </c>
       <c r="D150" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[1, 5, 17, 26, 38]</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2.1117</v>
+        <v>0.7524</v>
       </c>
       <c r="D151" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5578,14 +5578,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2.6835</v>
+        <v>1.0139</v>
       </c>
       <c r="D152" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5614,14 +5614,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2.6367</v>
+        <v>0.9782</v>
       </c>
       <c r="D153" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2.5406</v>
+        <v>1.0154</v>
       </c>
       <c r="D154" t="n">
         <v>121</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1.9904</v>
+        <v>0.8395</v>
       </c>
       <c r="D155" t="n">
         <v>115</v>
@@ -5722,14 +5722,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2.1415</v>
+        <v>0.9434</v>
       </c>
       <c r="D156" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5752,14 +5752,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 13, 26, 27, 38]</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2.1117</v>
+        <v>0.9325</v>
       </c>
       <c r="D157" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5782,14 +5782,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2.6835</v>
+        <v>1.0667</v>
       </c>
       <c r="D158" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -5818,14 +5818,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2.6367</v>
+        <v>1.0427</v>
       </c>
       <c r="D159" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2.5406</v>
+        <v>1.0731</v>
       </c>
       <c r="D160" t="n">
         <v>121</v>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1.9904</v>
+        <v>0.8831</v>
       </c>
       <c r="D161" t="n">
         <v>115</v>
@@ -5926,14 +5926,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 23, 26, 29]</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2.1415</v>
+        <v>1.0145</v>
       </c>
       <c r="D162" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5956,14 +5956,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 11, 15, 16, 37]</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2.1117</v>
+        <v>0.8582</v>
       </c>
       <c r="D163" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5986,14 +5986,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2.6835</v>
+        <v>1.1257</v>
       </c>
       <c r="D164" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -6022,14 +6022,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2.6367</v>
+        <v>1.1147</v>
       </c>
       <c r="D165" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>2.5406</v>
+        <v>1.1376</v>
       </c>
       <c r="D166" t="n">
         <v>121</v>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.9904</v>
+        <v>0.9319</v>
       </c>
       <c r="D167" t="n">
         <v>115</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2.1415</v>
+        <v>1.0222</v>
       </c>
       <c r="D168" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2.1117</v>
+        <v>0.8776</v>
       </c>
       <c r="D169" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2.6835</v>
+        <v>1.1944</v>
       </c>
       <c r="D170" t="n">
         <v>116</v>
@@ -6226,14 +6226,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2.6367</v>
+        <v>1.191</v>
       </c>
       <c r="D171" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2.5406</v>
+        <v>1.2088</v>
       </c>
       <c r="D172" t="n">
         <v>121</v>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1.9904</v>
+        <v>0.9856</v>
       </c>
       <c r="D173" t="n">
         <v>115</v>
@@ -6334,14 +6334,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2.1415</v>
+        <v>1.0683</v>
       </c>
       <c r="D174" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6364,14 +6364,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2.1117</v>
+        <v>0.9322</v>
       </c>
       <c r="D175" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2.6835</v>
+        <v>1.2828</v>
       </c>
       <c r="D176" t="n">
         <v>116</v>
@@ -6430,14 +6430,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>2.6367</v>
+        <v>1.2632</v>
       </c>
       <c r="D177" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2.5406</v>
+        <v>1.2878</v>
       </c>
       <c r="D178" t="n">
         <v>121</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1.9904</v>
+        <v>1.0452</v>
       </c>
       <c r="D179" t="n">
         <v>115</v>
@@ -6538,14 +6538,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2.1415</v>
+        <v>1.1193</v>
       </c>
       <c r="D180" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6568,14 +6568,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2.1117</v>
+        <v>0.9925</v>
       </c>
       <c r="D181" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2.6835</v>
+        <v>1.3812</v>
       </c>
       <c r="D182" t="n">
         <v>116</v>
@@ -6634,14 +6634,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[9, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2.6367</v>
+        <v>1.3439</v>
       </c>
       <c r="D183" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2.5406</v>
+        <v>1.3759</v>
       </c>
       <c r="D184" t="n">
         <v>121</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1.9904</v>
+        <v>1.1117</v>
       </c>
       <c r="D185" t="n">
         <v>115</v>
@@ -6742,14 +6742,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2.1415</v>
+        <v>1.1762</v>
       </c>
       <c r="D186" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2.1117</v>
+        <v>1.0599</v>
       </c>
       <c r="D187" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6802,14 +6802,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[10, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>2.6835</v>
+        <v>1.4996</v>
       </c>
       <c r="D188" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -6838,14 +6838,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2.6367</v>
+        <v>1.4905</v>
       </c>
       <c r="D189" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2.5406</v>
+        <v>1.4735</v>
       </c>
       <c r="D190" t="n">
         <v>121</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1.9904</v>
+        <v>1.1853</v>
       </c>
       <c r="D191" t="n">
         <v>115</v>
@@ -6946,14 +6946,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2.1415</v>
+        <v>1.2392</v>
       </c>
       <c r="D192" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6976,14 +6976,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2.1117</v>
+        <v>1.1344</v>
       </c>
       <c r="D193" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7006,14 +7006,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>[11, 17, 24, 26, 38]</t>
+          <t>[10, 14, 22, 28, 29]</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>2.6835</v>
+        <v>1.6156</v>
       </c>
       <c r="D194" t="n">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -7042,14 +7042,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>[10, 14, 22, 28, 29]</t>
+          <t>[11, 17, 24, 26, 38]</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>2.6367</v>
+        <v>1.6122</v>
       </c>
       <c r="D195" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2.5406</v>
+        <v>1.5824</v>
       </c>
       <c r="D196" t="n">
         <v>121</v>
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1.9904</v>
+        <v>1.2675</v>
       </c>
       <c r="D197" t="n">
         <v>115</v>
@@ -7150,14 +7150,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2.1415</v>
+        <v>1.3096</v>
       </c>
       <c r="D198" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7180,14 +7180,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[5, 12, 16, 25, 37]</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2.1117</v>
+        <v>1.2176</v>
       </c>
       <c r="D199" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2.6835</v>
+        <v>1.7473</v>
       </c>
       <c r="D200" t="n">
         <v>116</v>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>2.6367</v>
+        <v>1.7444</v>
       </c>
       <c r="D201" t="n">
         <v>103</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>2.5406</v>
+        <v>1.7032</v>
       </c>
       <c r="D202" t="n">
         <v>121</v>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1.9904</v>
+        <v>1.3587</v>
       </c>
       <c r="D203" t="n">
         <v>115</v>
@@ -7354,14 +7354,14 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2.1415</v>
+        <v>1.4423</v>
       </c>
       <c r="D204" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7384,14 +7384,14 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2.1117</v>
+        <v>1.3875</v>
       </c>
       <c r="D205" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2.6835</v>
+        <v>1.8975</v>
       </c>
       <c r="D206" t="n">
         <v>116</v>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>2.6367</v>
+        <v>1.8875</v>
       </c>
       <c r="D207" t="n">
         <v>103</v>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>2.5406</v>
+        <v>1.8376</v>
       </c>
       <c r="D208" t="n">
         <v>121</v>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1.9904</v>
+        <v>1.4601</v>
       </c>
       <c r="D209" t="n">
         <v>115</v>
@@ -7558,14 +7558,14 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>2.1415</v>
+        <v>1.5498</v>
       </c>
       <c r="D210" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7588,14 +7588,14 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>2.1117</v>
+        <v>1.4744</v>
       </c>
       <c r="D211" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>2.6835</v>
+        <v>2.0645</v>
       </c>
       <c r="D212" t="n">
         <v>116</v>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>2.6367</v>
+        <v>2.0468</v>
       </c>
       <c r="D213" t="n">
         <v>103</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>2.5406</v>
+        <v>1.987</v>
       </c>
       <c r="D214" t="n">
         <v>121</v>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1.9904</v>
+        <v>1.5728</v>
       </c>
       <c r="D215" t="n">
         <v>115</v>
@@ -7762,14 +7762,14 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2.1415</v>
+        <v>1.6693</v>
       </c>
       <c r="D216" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>2.1117</v>
+        <v>1.5708</v>
       </c>
       <c r="D217" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>2.6835</v>
+        <v>2.2494</v>
       </c>
       <c r="D218" t="n">
         <v>116</v>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>2.6367</v>
+        <v>2.2229</v>
       </c>
       <c r="D219" t="n">
         <v>103</v>
@@ -7898,7 +7898,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>2.5406</v>
+        <v>2.1523</v>
       </c>
       <c r="D220" t="n">
         <v>121</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>1.9904</v>
+        <v>1.6975</v>
       </c>
       <c r="D221" t="n">
         <v>115</v>
@@ -7966,14 +7966,14 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>2.1415</v>
+        <v>1.8014</v>
       </c>
       <c r="D222" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7996,14 +7996,14 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>2.1117</v>
+        <v>1.6775</v>
       </c>
       <c r="D223" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>2.6835</v>
+        <v>2.2494</v>
       </c>
       <c r="D224" t="n">
         <v>116</v>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2.6367</v>
+        <v>2.2229</v>
       </c>
       <c r="D225" t="n">
         <v>103</v>
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>2.5406</v>
+        <v>2.1523</v>
       </c>
       <c r="D226" t="n">
         <v>121</v>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>1.9904</v>
+        <v>1.6975</v>
       </c>
       <c r="D227" t="n">
         <v>115</v>
@@ -8170,14 +8170,14 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[10, 12, 25, 26, 29]</t>
+          <t>[5, 12, 16, 26, 37]</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>2.1415</v>
+        <v>1.8014</v>
       </c>
       <c r="D228" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -8200,14 +8200,14 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>[5, 12, 16, 26, 37]</t>
+          <t>[10, 11, 25, 26, 29]</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2.1117</v>
+        <v>1.6775</v>
       </c>
       <c r="D229" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>2.6835</v>
+        <v>2.455</v>
       </c>
       <c r="D230" t="n">
         <v>116</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2.6367</v>
+        <v>2.4189</v>
       </c>
       <c r="D231" t="n">
         <v>103</v>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>2.5406</v>
+        <v>2.3362</v>
       </c>
       <c r="D232" t="n">
         <v>121</v>
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1.9904</v>
+        <v>1.8362</v>
       </c>
       <c r="D233" t="n">
         <v>115</v>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>2.1415</v>
+        <v>1.9843</v>
       </c>
       <c r="D234" t="n">
         <v>102</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>2.1117</v>
+        <v>1.9484</v>
       </c>
       <c r="D235" t="n">
         <v>96</v>
@@ -9241,6 +9241,3066 @@
       </c>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D260" t="n">
+        <v>116</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>3</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D261" t="n">
+        <v>103</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>15</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D262" t="n">
+        <v>121</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>13</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D263" t="n">
+        <v>115</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>10</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D264" t="n">
+        <v>102</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D265" t="n">
+        <v>96</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D266" t="n">
+        <v>116</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>3</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D267" t="n">
+        <v>103</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>15</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D268" t="n">
+        <v>121</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>13</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D269" t="n">
+        <v>115</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>10</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D270" t="n">
+        <v>102</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D271" t="n">
+        <v>96</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D272" t="n">
+        <v>116</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>3</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D273" t="n">
+        <v>103</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>15</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D274" t="n">
+        <v>121</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>13</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D275" t="n">
+        <v>115</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>10</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D276" t="n">
+        <v>102</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D277" t="n">
+        <v>96</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D278" t="n">
+        <v>116</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>3</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D279" t="n">
+        <v>103</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>15</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D280" t="n">
+        <v>121</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>13</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D281" t="n">
+        <v>115</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>10</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D282" t="n">
+        <v>102</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D283" t="n">
+        <v>96</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D284" t="n">
+        <v>116</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>3</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D285" t="n">
+        <v>103</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>15</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D286" t="n">
+        <v>121</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>13</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D287" t="n">
+        <v>115</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>10</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D288" t="n">
+        <v>102</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D289" t="n">
+        <v>96</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D290" t="n">
+        <v>116</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>3</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D291" t="n">
+        <v>103</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>15</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D292" t="n">
+        <v>121</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>13</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D293" t="n">
+        <v>115</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>10</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D294" t="n">
+        <v>102</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D295" t="n">
+        <v>96</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D296" t="n">
+        <v>116</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>3</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D297" t="n">
+        <v>103</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>15</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D298" t="n">
+        <v>121</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>13</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D299" t="n">
+        <v>115</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>10</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D300" t="n">
+        <v>102</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D301" t="n">
+        <v>96</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D302" t="n">
+        <v>116</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>3</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D303" t="n">
+        <v>103</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>15</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D304" t="n">
+        <v>121</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>13</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D305" t="n">
+        <v>115</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>10</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D306" t="n">
+        <v>102</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D307" t="n">
+        <v>96</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D308" t="n">
+        <v>116</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>3</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D309" t="n">
+        <v>103</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>15</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D310" t="n">
+        <v>121</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>13</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D311" t="n">
+        <v>115</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>10</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D312" t="n">
+        <v>102</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D313" t="n">
+        <v>96</v>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D314" t="n">
+        <v>116</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>3</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D315" t="n">
+        <v>103</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>15</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D316" t="n">
+        <v>121</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>13</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D317" t="n">
+        <v>115</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>10</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D318" t="n">
+        <v>102</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D319" t="n">
+        <v>96</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D320" t="n">
+        <v>116</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>3</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D321" t="n">
+        <v>103</v>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>15</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D322" t="n">
+        <v>121</v>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>13</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D323" t="n">
+        <v>115</v>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>10</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D324" t="n">
+        <v>102</v>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D325" t="n">
+        <v>96</v>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D326" t="n">
+        <v>116</v>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>3</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D327" t="n">
+        <v>103</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>15</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D328" t="n">
+        <v>121</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>13</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D329" t="n">
+        <v>115</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>10</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D330" t="n">
+        <v>102</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D331" t="n">
+        <v>96</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D332" t="n">
+        <v>116</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>3</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D333" t="n">
+        <v>103</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>15</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D334" t="n">
+        <v>121</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>13</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D335" t="n">
+        <v>115</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>10</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D336" t="n">
+        <v>102</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D337" t="n">
+        <v>96</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D338" t="n">
+        <v>116</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>3</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D339" t="n">
+        <v>103</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>15</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D340" t="n">
+        <v>121</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>13</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D341" t="n">
+        <v>115</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>10</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D342" t="n">
+        <v>102</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D343" t="n">
+        <v>96</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>[11, 17, 24, 26, 38]</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>2.6835</v>
+      </c>
+      <c r="D344" t="n">
+        <v>116</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>3</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>BALOTO</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>[10, 14, 22, 28, 29]</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>2.6367</v>
+      </c>
+      <c r="D345" t="n">
+        <v>103</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>15</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>[15, 18, 22, 28, 38]</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>2.5406</v>
+      </c>
+      <c r="D346" t="n">
+        <v>121</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>13</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>REVANCHA</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>[8, 9, 22, 37, 39]</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>1.9904</v>
+      </c>
+      <c r="D347" t="n">
+        <v>115</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>10</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>SuperBalota</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>[10, 12, 25, 26, 29]</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>2.1415</v>
+      </c>
+      <c r="D348" t="n">
+        <v>102</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>MILOTO</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>[5, 12, 16, 26, 37]</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>2.1117</v>
+      </c>
+      <c r="D349" t="n">
+        <v>96</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>LOOP-MULTI</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
